--- a/data/trans_bre/P1002-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1002-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,41</t>
+          <t>-0,25; 6,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 6,55</t>
+          <t>-0,46; 7,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 5,07</t>
+          <t>-1,09; 5,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,9</t>
+          <t>-0,9; 5,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 205,52</t>
+          <t>-8,17; 256,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 243,8</t>
+          <t>-12,85; 272,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 200,66</t>
+          <t>-24,2; 219,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 147,91</t>
+          <t>-18,97; 141,97</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 7,14</t>
+          <t>0,05; 6,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 8,75</t>
+          <t>0,55; 8,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,67</t>
+          <t>-1,94; 4,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,52</t>
+          <t>2,68; 8,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 313,72</t>
+          <t>-7,4; 343,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 257,31</t>
+          <t>-4,04; 243,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,29; 188,15</t>
+          <t>-39,21; 158,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>61,94; 561,27</t>
+          <t>62,45; 572,53</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 10,45</t>
+          <t>0,38; 10,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 13,8</t>
+          <t>3,56; 14,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 15,0</t>
+          <t>2,93; 15,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 11,35</t>
+          <t>-0,35; 11,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 243,44</t>
+          <t>0,79; 262,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,82; 195,17</t>
+          <t>29,45; 192,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,93; 310,39</t>
+          <t>35,9; 318,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 431,82</t>
+          <t>-6,26; 505,75</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 4,42</t>
+          <t>-0,57; 4,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,57</t>
+          <t>0,64; 6,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,45</t>
+          <t>2,3; 7,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 2,42</t>
+          <t>-3,76; 2,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 78,3</t>
+          <t>-7,27; 78,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 88,62</t>
+          <t>7,24; 87,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,84; 169,71</t>
+          <t>34,69; 161,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 41,59</t>
+          <t>-50,74; 44,82</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 6,65</t>
+          <t>-0,52; 6,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,63; 16,65</t>
+          <t>9,65; 17,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 10,52</t>
+          <t>4,32; 10,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,6</t>
+          <t>1,0; 8,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 183,28</t>
+          <t>-7,38; 158,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>126,33; 391,43</t>
+          <t>121,11; 400,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,78; 181,72</t>
+          <t>50,11; 183,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 140,0</t>
+          <t>11,98; 139,5</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,99</t>
+          <t>2,77; 8,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,23; 13,18</t>
+          <t>6,31; 12,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,24; 10,38</t>
+          <t>4,53; 10,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,41; 12,89</t>
+          <t>4,35; 12,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,16; 452,69</t>
+          <t>45,72; 415,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,57; 546,86</t>
+          <t>83,04; 527,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67,61; 532,48</t>
+          <t>77,78; 577,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,54; 648,89</t>
+          <t>45,9; 637,69</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,54</t>
+          <t>2,03; 4,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 8,83</t>
+          <t>5,71; 8,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,85</t>
+          <t>4,06; 6,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,13</t>
+          <t>2,5; 6,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,05; 97,93</t>
+          <t>36,17; 97,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,04; 146,33</t>
+          <t>76,84; 144,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,04; 145,3</t>
+          <t>67,42; 140,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>42,65; 134,31</t>
+          <t>43,11; 138,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1002-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1002-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>57,04%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 6,03</t>
+          <t>-0,36; 6,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 7,18</t>
+          <t>-0,22; 7,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 5,23</t>
+          <t>-1,38; 5,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,02</t>
+          <t>-0,55; 5,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 256,45</t>
+          <t>-13,58; 256,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 272,83</t>
+          <t>-13,51; 255,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 219,74</t>
+          <t>-28,69; 183,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 141,97</t>
+          <t>-11,64; 151,6</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>226,45%</t>
+          <t>216,3%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 6,93</t>
+          <t>0,1; 6,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 8,77</t>
+          <t>0,34; 8,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,55</t>
+          <t>-1,93; 4,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 8,62</t>
+          <t>2,94; 8,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 343,85</t>
+          <t>-0,08; 369,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 243,84</t>
+          <t>3,24; 238,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,21; 158,33</t>
+          <t>-38,19; 181,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>62,45; 572,53</t>
+          <t>70,37; 585,05</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 10,78</t>
+          <t>0,3; 10,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,25</t>
+          <t>3,32; 14,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 15,94</t>
+          <t>2,42; 15,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 11,1</t>
+          <t>-2,59; 5,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 262,45</t>
+          <t>0,95; 255,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,45; 192,67</t>
+          <t>32,85; 207,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,9; 318,28</t>
+          <t>28,13; 309,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 505,75</t>
+          <t>-27,23; 104,1</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,64</t>
+          <t>-0,59; 4,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,28</t>
+          <t>0,74; 6,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,45</t>
+          <t>2,23; 7,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,63</t>
+          <t>-0,25; 3,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 78,89</t>
+          <t>-8,14; 77,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 87,35</t>
+          <t>8,1; 92,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,69; 161,89</t>
+          <t>37,54; 162,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 44,82</t>
+          <t>-3,28; 72,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 6,49</t>
+          <t>-0,44; 6,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,65; 17,0</t>
+          <t>10,04; 17,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,77</t>
+          <t>3,77; 10,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,52</t>
+          <t>3,81; 9,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 158,67</t>
+          <t>-8,39; 155,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>121,11; 400,52</t>
+          <t>125,72; 406,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,11; 183,45</t>
+          <t>39,19; 177,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 139,5</t>
+          <t>41,86; 179,2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,38</t>
+          <t>8,27</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>205,44%</t>
+          <t>154,55%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,01</t>
+          <t>2,76; 8,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,99</t>
+          <t>7,02; 13,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,44</t>
+          <t>4,5; 10,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,65</t>
+          <t>2,04; 11,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,72; 415,13</t>
+          <t>47,57; 454,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83,04; 527,05</t>
+          <t>90,23; 599,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,78; 577,68</t>
+          <t>74,41; 522,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,9; 637,69</t>
+          <t>12,53; 493,76</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,46</t>
+          <t>1,93; 4,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,71; 8,81</t>
+          <t>5,85; 8,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,71</t>
+          <t>4,12; 6,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,05</t>
+          <t>3,55; 6,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,17; 97,56</t>
+          <t>32,86; 95,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,84; 144,35</t>
+          <t>79,98; 146,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,42; 140,33</t>
+          <t>70,22; 144,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,11; 138,91</t>
+          <t>56,1; 121,54</t>
         </is>
       </c>
     </row>
